--- a/Documentation/GanntChart/BattleNationsGanntChart-1.02.xlsx
+++ b/Documentation/GanntChart/BattleNationsGanntChart-1.02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jreig\git\BattleNations\Documentation\GanntChart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E93C66C-D94C-414D-A9A7-E78BC04D21A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FB9807-2724-4697-9156-D7400EEC3F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="142">
   <si>
     <t/>
   </si>
@@ -6475,7 +6475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DE43"/>
+  <dimension ref="A1:DE44"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="52.83203125" customWidth="1"/>
@@ -11201,17 +11201,19 @@
     </row>
     <row r="35" spans="1:109" x14ac:dyDescent="0.8">
       <c r="A35" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="227" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="228" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="228"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="230" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="488">
+        <v>46101</v>
+      </c>
+      <c r="C35" s="489">
+        <v>46108</v>
+      </c>
+      <c r="D35" s="492">
+        <v>0.3</v>
+      </c>
+      <c r="E35" s="225"/>
+      <c r="F35" s="226" t="s">
         <v>0</v>
       </c>
       <c r="G35" s="2"/>
@@ -11237,36 +11239,36 @@
       <c r="AA35" s="2"/>
       <c r="AB35" s="2"/>
       <c r="AC35" s="2"/>
-      <c r="AD35" s="2"/>
-      <c r="AE35" s="2"/>
-      <c r="AF35" s="2"/>
-      <c r="AG35" s="2"/>
-      <c r="AH35" s="2"/>
-      <c r="AI35" s="2"/>
-      <c r="AJ35" s="333" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK35" s="334" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL35" s="335" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM35" s="336" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN35" s="337" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO35" s="338" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP35" s="339" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ35" s="340" t="s">
-        <v>81</v>
-      </c>
+      <c r="AD35" s="325" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE35" s="326" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF35" s="327" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG35" s="328" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH35" s="329" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI35" s="330" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ35" s="331" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK35" s="332" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL35" s="2"/>
+      <c r="AM35" s="2"/>
+      <c r="AN35" s="2"/>
+      <c r="AO35" s="2"/>
+      <c r="AP35" s="2"/>
+      <c r="AQ35" s="2"/>
       <c r="AR35" s="2"/>
       <c r="AS35" s="2"/>
       <c r="AT35" s="2"/>
@@ -11336,17 +11338,17 @@
     </row>
     <row r="36" spans="1:109" x14ac:dyDescent="0.8">
       <c r="A36" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B36" s="231" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" s="232" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="232"/>
-      <c r="E36" s="233"/>
-      <c r="F36" s="234" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="227" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="228" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="228"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="230" t="s">
         <v>0</v>
       </c>
       <c r="G36" s="2"/>
@@ -11378,39 +11380,39 @@
       <c r="AG36" s="2"/>
       <c r="AH36" s="2"/>
       <c r="AI36" s="2"/>
-      <c r="AJ36" s="2"/>
-      <c r="AK36" s="2"/>
-      <c r="AL36" s="2"/>
-      <c r="AM36" s="2"/>
-      <c r="AN36" s="2"/>
-      <c r="AO36" s="2"/>
-      <c r="AP36" s="2"/>
-      <c r="AQ36" s="2"/>
+      <c r="AJ36" s="333" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK36" s="334" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL36" s="335" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM36" s="336" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN36" s="337" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO36" s="338" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP36" s="339" t="s">
+        <v>81</v>
+      </c>
+      <c r="AQ36" s="340" t="s">
+        <v>81</v>
+      </c>
       <c r="AR36" s="2"/>
-      <c r="AS36" s="341" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT36" s="342" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU36" s="343" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV36" s="344" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW36" s="345" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX36" s="346" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY36" s="347" t="s">
-        <v>85</v>
-      </c>
-      <c r="AZ36" s="348" t="s">
-        <v>85</v>
-      </c>
+      <c r="AS36" s="2"/>
+      <c r="AT36" s="2"/>
+      <c r="AU36" s="2"/>
+      <c r="AV36" s="2"/>
+      <c r="AW36" s="2"/>
+      <c r="AX36" s="2"/>
+      <c r="AY36" s="2"/>
+      <c r="AZ36" s="2"/>
       <c r="BA36" s="2"/>
       <c r="BB36" s="2"/>
       <c r="BC36" s="2"/>
@@ -11471,17 +11473,17 @@
     </row>
     <row r="37" spans="1:109" x14ac:dyDescent="0.8">
       <c r="A37" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" s="235" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="231" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="232" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="236" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" s="236"/>
-      <c r="E37" s="237"/>
-      <c r="F37" s="238" t="s">
+      <c r="D37" s="232"/>
+      <c r="E37" s="233"/>
+      <c r="F37" s="234" t="s">
         <v>0</v>
       </c>
       <c r="G37" s="2"/>
@@ -11522,58 +11524,44 @@
       <c r="AP37" s="2"/>
       <c r="AQ37" s="2"/>
       <c r="AR37" s="2"/>
-      <c r="AS37" s="2"/>
-      <c r="AT37" s="2"/>
-      <c r="AU37" s="2"/>
-      <c r="AV37" s="2"/>
-      <c r="AW37" s="2"/>
-      <c r="AX37" s="2"/>
-      <c r="AY37" s="2"/>
-      <c r="AZ37" s="349" t="s">
-        <v>88</v>
-      </c>
-      <c r="BA37" s="350" t="s">
-        <v>88</v>
-      </c>
-      <c r="BB37" s="351" t="s">
-        <v>88</v>
-      </c>
-      <c r="BC37" s="352" t="s">
-        <v>88</v>
-      </c>
-      <c r="BD37" s="353" t="s">
-        <v>88</v>
-      </c>
-      <c r="BE37" s="354" t="s">
-        <v>88</v>
-      </c>
-      <c r="BF37" s="355" t="s">
-        <v>88</v>
-      </c>
-      <c r="BG37" s="356" t="s">
-        <v>88</v>
-      </c>
-      <c r="BH37" s="357" t="s">
-        <v>88</v>
-      </c>
-      <c r="BI37" s="358" t="s">
-        <v>88</v>
-      </c>
-      <c r="BJ37" s="359" t="s">
-        <v>88</v>
-      </c>
-      <c r="BK37" s="360" t="s">
-        <v>88</v>
-      </c>
-      <c r="BL37" s="361" t="s">
-        <v>88</v>
-      </c>
-      <c r="BM37" s="362" t="s">
-        <v>88</v>
-      </c>
-      <c r="BN37" s="363" t="s">
-        <v>88</v>
-      </c>
+      <c r="AS37" s="341" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT37" s="342" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU37" s="343" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV37" s="344" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW37" s="345" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX37" s="346" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY37" s="347" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ37" s="348" t="s">
+        <v>85</v>
+      </c>
+      <c r="BA37" s="2"/>
+      <c r="BB37" s="2"/>
+      <c r="BC37" s="2"/>
+      <c r="BD37" s="2"/>
+      <c r="BE37" s="2"/>
+      <c r="BF37" s="2"/>
+      <c r="BG37" s="2"/>
+      <c r="BH37" s="2"/>
+      <c r="BI37" s="2"/>
+      <c r="BJ37" s="2"/>
+      <c r="BK37" s="2"/>
+      <c r="BL37" s="2"/>
+      <c r="BM37" s="2"/>
+      <c r="BN37" s="2"/>
       <c r="BO37" s="2"/>
       <c r="BP37" s="2"/>
       <c r="BQ37" s="2"/>
@@ -11620,17 +11608,17 @@
     </row>
     <row r="38" spans="1:109" x14ac:dyDescent="0.8">
       <c r="A38" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" s="239" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="240" t="s">
+      <c r="C38" s="236" t="s">
         <v>87</v>
       </c>
-      <c r="D38" s="240"/>
-      <c r="E38" s="241"/>
-      <c r="F38" s="242" t="s">
+      <c r="D38" s="236"/>
+      <c r="E38" s="237"/>
+      <c r="F38" s="238" t="s">
         <v>0</v>
       </c>
       <c r="G38" s="2"/>
@@ -11678,50 +11666,50 @@
       <c r="AW38" s="2"/>
       <c r="AX38" s="2"/>
       <c r="AY38" s="2"/>
-      <c r="AZ38" s="364" t="s">
-        <v>90</v>
-      </c>
-      <c r="BA38" s="365" t="s">
-        <v>90</v>
-      </c>
-      <c r="BB38" s="366" t="s">
-        <v>90</v>
-      </c>
-      <c r="BC38" s="367" t="s">
-        <v>90</v>
-      </c>
-      <c r="BD38" s="368" t="s">
-        <v>90</v>
-      </c>
-      <c r="BE38" s="369" t="s">
-        <v>90</v>
-      </c>
-      <c r="BF38" s="370" t="s">
-        <v>90</v>
-      </c>
-      <c r="BG38" s="371" t="s">
-        <v>90</v>
-      </c>
-      <c r="BH38" s="372" t="s">
-        <v>90</v>
-      </c>
-      <c r="BI38" s="373" t="s">
-        <v>90</v>
-      </c>
-      <c r="BJ38" s="374" t="s">
-        <v>90</v>
-      </c>
-      <c r="BK38" s="375" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL38" s="376" t="s">
-        <v>90</v>
-      </c>
-      <c r="BM38" s="377" t="s">
-        <v>90</v>
-      </c>
-      <c r="BN38" s="378" t="s">
-        <v>90</v>
+      <c r="AZ38" s="349" t="s">
+        <v>88</v>
+      </c>
+      <c r="BA38" s="350" t="s">
+        <v>88</v>
+      </c>
+      <c r="BB38" s="351" t="s">
+        <v>88</v>
+      </c>
+      <c r="BC38" s="352" t="s">
+        <v>88</v>
+      </c>
+      <c r="BD38" s="353" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE38" s="354" t="s">
+        <v>88</v>
+      </c>
+      <c r="BF38" s="355" t="s">
+        <v>88</v>
+      </c>
+      <c r="BG38" s="356" t="s">
+        <v>88</v>
+      </c>
+      <c r="BH38" s="357" t="s">
+        <v>88</v>
+      </c>
+      <c r="BI38" s="358" t="s">
+        <v>88</v>
+      </c>
+      <c r="BJ38" s="359" t="s">
+        <v>88</v>
+      </c>
+      <c r="BK38" s="360" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL38" s="361" t="s">
+        <v>88</v>
+      </c>
+      <c r="BM38" s="362" t="s">
+        <v>88</v>
+      </c>
+      <c r="BN38" s="363" t="s">
+        <v>88</v>
       </c>
       <c r="BO38" s="2"/>
       <c r="BP38" s="2"/>
@@ -11769,17 +11757,17 @@
     </row>
     <row r="39" spans="1:109" x14ac:dyDescent="0.8">
       <c r="A39" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="243" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="239" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="244" t="s">
+      <c r="C39" s="240" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="244"/>
-      <c r="E39" s="245"/>
-      <c r="F39" s="246" t="s">
+      <c r="D39" s="240"/>
+      <c r="E39" s="241"/>
+      <c r="F39" s="242" t="s">
         <v>0</v>
       </c>
       <c r="G39" s="2"/>
@@ -11827,50 +11815,50 @@
       <c r="AW39" s="2"/>
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
-      <c r="AZ39" s="379" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA39" s="380" t="s">
-        <v>92</v>
-      </c>
-      <c r="BB39" s="381" t="s">
-        <v>92</v>
-      </c>
-      <c r="BC39" s="382" t="s">
-        <v>92</v>
-      </c>
-      <c r="BD39" s="383" t="s">
-        <v>92</v>
-      </c>
-      <c r="BE39" s="384" t="s">
-        <v>92</v>
-      </c>
-      <c r="BF39" s="385" t="s">
-        <v>92</v>
-      </c>
-      <c r="BG39" s="386" t="s">
-        <v>92</v>
-      </c>
-      <c r="BH39" s="387" t="s">
-        <v>92</v>
-      </c>
-      <c r="BI39" s="388" t="s">
-        <v>92</v>
-      </c>
-      <c r="BJ39" s="389" t="s">
-        <v>92</v>
-      </c>
-      <c r="BK39" s="390" t="s">
-        <v>92</v>
-      </c>
-      <c r="BL39" s="391" t="s">
-        <v>92</v>
-      </c>
-      <c r="BM39" s="392" t="s">
-        <v>92</v>
-      </c>
-      <c r="BN39" s="393" t="s">
-        <v>92</v>
+      <c r="AZ39" s="364" t="s">
+        <v>90</v>
+      </c>
+      <c r="BA39" s="365" t="s">
+        <v>90</v>
+      </c>
+      <c r="BB39" s="366" t="s">
+        <v>90</v>
+      </c>
+      <c r="BC39" s="367" t="s">
+        <v>90</v>
+      </c>
+      <c r="BD39" s="368" t="s">
+        <v>90</v>
+      </c>
+      <c r="BE39" s="369" t="s">
+        <v>90</v>
+      </c>
+      <c r="BF39" s="370" t="s">
+        <v>90</v>
+      </c>
+      <c r="BG39" s="371" t="s">
+        <v>90</v>
+      </c>
+      <c r="BH39" s="372" t="s">
+        <v>90</v>
+      </c>
+      <c r="BI39" s="373" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ39" s="374" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK39" s="375" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL39" s="376" t="s">
+        <v>90</v>
+      </c>
+      <c r="BM39" s="377" t="s">
+        <v>90</v>
+      </c>
+      <c r="BN39" s="378" t="s">
+        <v>90</v>
       </c>
       <c r="BO39" s="2"/>
       <c r="BP39" s="2"/>
@@ -11918,17 +11906,17 @@
     </row>
     <row r="40" spans="1:109" x14ac:dyDescent="0.8">
       <c r="A40" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" s="247" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="243" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="248" t="s">
+      <c r="C40" s="244" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="248"/>
-      <c r="E40" s="249"/>
-      <c r="F40" s="250" t="s">
+      <c r="D40" s="244"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="246" t="s">
         <v>0</v>
       </c>
       <c r="G40" s="2"/>
@@ -11976,50 +11964,50 @@
       <c r="AW40" s="2"/>
       <c r="AX40" s="2"/>
       <c r="AY40" s="2"/>
-      <c r="AZ40" s="394" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA40" s="395" t="s">
-        <v>94</v>
-      </c>
-      <c r="BB40" s="396" t="s">
-        <v>94</v>
-      </c>
-      <c r="BC40" s="397" t="s">
-        <v>94</v>
-      </c>
-      <c r="BD40" s="398" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE40" s="399" t="s">
-        <v>94</v>
-      </c>
-      <c r="BF40" s="400" t="s">
-        <v>94</v>
-      </c>
-      <c r="BG40" s="401" t="s">
-        <v>94</v>
-      </c>
-      <c r="BH40" s="402" t="s">
-        <v>94</v>
-      </c>
-      <c r="BI40" s="403" t="s">
-        <v>94</v>
-      </c>
-      <c r="BJ40" s="404" t="s">
-        <v>94</v>
-      </c>
-      <c r="BK40" s="405" t="s">
-        <v>94</v>
-      </c>
-      <c r="BL40" s="406" t="s">
-        <v>94</v>
-      </c>
-      <c r="BM40" s="407" t="s">
-        <v>94</v>
-      </c>
-      <c r="BN40" s="408" t="s">
-        <v>94</v>
+      <c r="AZ40" s="379" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA40" s="380" t="s">
+        <v>92</v>
+      </c>
+      <c r="BB40" s="381" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC40" s="382" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD40" s="383" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE40" s="384" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF40" s="385" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG40" s="386" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH40" s="387" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI40" s="388" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ40" s="389" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK40" s="390" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL40" s="391" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM40" s="392" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN40" s="393" t="s">
+        <v>92</v>
       </c>
       <c r="BO40" s="2"/>
       <c r="BP40" s="2"/>
@@ -12067,17 +12055,17 @@
     </row>
     <row r="41" spans="1:109" x14ac:dyDescent="0.8">
       <c r="A41" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41" s="251" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" s="252" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" s="252"/>
-      <c r="E41" s="253"/>
-      <c r="F41" s="254" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="247" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="248" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="248"/>
+      <c r="E41" s="249"/>
+      <c r="F41" s="250" t="s">
         <v>0</v>
       </c>
       <c r="G41" s="2"/>
@@ -12125,39 +12113,51 @@
       <c r="AW41" s="2"/>
       <c r="AX41" s="2"/>
       <c r="AY41" s="2"/>
-      <c r="AZ41" s="2"/>
-      <c r="BA41" s="2"/>
-      <c r="BB41" s="2"/>
-      <c r="BC41" s="2"/>
-      <c r="BD41" s="409" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE41" s="410" t="s">
-        <v>98</v>
-      </c>
-      <c r="BF41" s="411" t="s">
-        <v>98</v>
-      </c>
-      <c r="BG41" s="412" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH41" s="413" t="s">
-        <v>98</v>
-      </c>
-      <c r="BI41" s="414" t="s">
-        <v>98</v>
-      </c>
-      <c r="BJ41" s="415" t="s">
-        <v>98</v>
-      </c>
-      <c r="BK41" s="416" t="s">
-        <v>98</v>
-      </c>
-      <c r="BL41" s="417" t="s">
-        <v>98</v>
-      </c>
-      <c r="BM41" s="2"/>
-      <c r="BN41" s="2"/>
+      <c r="AZ41" s="394" t="s">
+        <v>94</v>
+      </c>
+      <c r="BA41" s="395" t="s">
+        <v>94</v>
+      </c>
+      <c r="BB41" s="396" t="s">
+        <v>94</v>
+      </c>
+      <c r="BC41" s="397" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD41" s="398" t="s">
+        <v>94</v>
+      </c>
+      <c r="BE41" s="399" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF41" s="400" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG41" s="401" t="s">
+        <v>94</v>
+      </c>
+      <c r="BH41" s="402" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI41" s="403" t="s">
+        <v>94</v>
+      </c>
+      <c r="BJ41" s="404" t="s">
+        <v>94</v>
+      </c>
+      <c r="BK41" s="405" t="s">
+        <v>94</v>
+      </c>
+      <c r="BL41" s="406" t="s">
+        <v>94</v>
+      </c>
+      <c r="BM41" s="407" t="s">
+        <v>94</v>
+      </c>
+      <c r="BN41" s="408" t="s">
+        <v>94</v>
+      </c>
       <c r="BO41" s="2"/>
       <c r="BP41" s="2"/>
       <c r="BQ41" s="2"/>
@@ -12204,17 +12204,17 @@
     </row>
     <row r="42" spans="1:109" x14ac:dyDescent="0.8">
       <c r="A42" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B42" s="255" t="s">
-        <v>100</v>
-      </c>
-      <c r="C42" s="256" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" s="256"/>
-      <c r="E42" s="257"/>
-      <c r="F42" s="258" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="251" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" s="252" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" s="252"/>
+      <c r="E42" s="253"/>
+      <c r="F42" s="254" t="s">
         <v>0</v>
       </c>
       <c r="G42" s="2"/>
@@ -12266,46 +12266,42 @@
       <c r="BA42" s="2"/>
       <c r="BB42" s="2"/>
       <c r="BC42" s="2"/>
-      <c r="BD42" s="2"/>
-      <c r="BE42" s="2"/>
-      <c r="BF42" s="2"/>
-      <c r="BG42" s="2"/>
-      <c r="BH42" s="2"/>
-      <c r="BI42" s="2"/>
-      <c r="BJ42" s="2"/>
-      <c r="BK42" s="418" t="s">
-        <v>102</v>
-      </c>
-      <c r="BL42" s="419" t="s">
-        <v>102</v>
-      </c>
-      <c r="BM42" s="420" t="s">
-        <v>102</v>
-      </c>
-      <c r="BN42" s="421" t="s">
-        <v>102</v>
-      </c>
-      <c r="BO42" s="422" t="s">
-        <v>102</v>
-      </c>
-      <c r="BP42" s="423" t="s">
-        <v>102</v>
-      </c>
-      <c r="BQ42" s="424" t="s">
-        <v>102</v>
-      </c>
-      <c r="BR42" s="425" t="s">
-        <v>102</v>
-      </c>
-      <c r="BS42" s="426" t="s">
-        <v>102</v>
-      </c>
-      <c r="BT42" s="427" t="s">
-        <v>102</v>
-      </c>
-      <c r="BU42" s="428" t="s">
-        <v>102</v>
-      </c>
+      <c r="BD42" s="409" t="s">
+        <v>98</v>
+      </c>
+      <c r="BE42" s="410" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF42" s="411" t="s">
+        <v>98</v>
+      </c>
+      <c r="BG42" s="412" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH42" s="413" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI42" s="414" t="s">
+        <v>98</v>
+      </c>
+      <c r="BJ42" s="415" t="s">
+        <v>98</v>
+      </c>
+      <c r="BK42" s="416" t="s">
+        <v>98</v>
+      </c>
+      <c r="BL42" s="417" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM42" s="2"/>
+      <c r="BN42" s="2"/>
+      <c r="BO42" s="2"/>
+      <c r="BP42" s="2"/>
+      <c r="BQ42" s="2"/>
+      <c r="BR42" s="2"/>
+      <c r="BS42" s="2"/>
+      <c r="BT42" s="2"/>
+      <c r="BU42" s="2"/>
       <c r="BV42" s="2"/>
       <c r="BW42" s="2"/>
       <c r="BX42" s="2"/>
@@ -12345,17 +12341,17 @@
     </row>
     <row r="43" spans="1:109" x14ac:dyDescent="0.8">
       <c r="A43" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B43" s="259" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="255" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="260" t="s">
+      <c r="C43" s="256" t="s">
         <v>101</v>
       </c>
-      <c r="D43" s="260"/>
-      <c r="E43" s="261"/>
-      <c r="F43" s="262" t="s">
+      <c r="D43" s="256"/>
+      <c r="E43" s="257"/>
+      <c r="F43" s="258" t="s">
         <v>0</v>
       </c>
       <c r="G43" s="2"/>
@@ -12414,38 +12410,38 @@
       <c r="BH43" s="2"/>
       <c r="BI43" s="2"/>
       <c r="BJ43" s="2"/>
-      <c r="BK43" s="429" t="s">
-        <v>104</v>
-      </c>
-      <c r="BL43" s="430" t="s">
-        <v>104</v>
-      </c>
-      <c r="BM43" s="431" t="s">
-        <v>104</v>
-      </c>
-      <c r="BN43" s="432" t="s">
-        <v>104</v>
-      </c>
-      <c r="BO43" s="433" t="s">
-        <v>104</v>
-      </c>
-      <c r="BP43" s="434" t="s">
-        <v>104</v>
-      </c>
-      <c r="BQ43" s="435" t="s">
-        <v>104</v>
-      </c>
-      <c r="BR43" s="436" t="s">
-        <v>104</v>
-      </c>
-      <c r="BS43" s="437" t="s">
-        <v>104</v>
-      </c>
-      <c r="BT43" s="438" t="s">
-        <v>104</v>
-      </c>
-      <c r="BU43" s="439" t="s">
-        <v>104</v>
+      <c r="BK43" s="418" t="s">
+        <v>102</v>
+      </c>
+      <c r="BL43" s="419" t="s">
+        <v>102</v>
+      </c>
+      <c r="BM43" s="420" t="s">
+        <v>102</v>
+      </c>
+      <c r="BN43" s="421" t="s">
+        <v>102</v>
+      </c>
+      <c r="BO43" s="422" t="s">
+        <v>102</v>
+      </c>
+      <c r="BP43" s="423" t="s">
+        <v>102</v>
+      </c>
+      <c r="BQ43" s="424" t="s">
+        <v>102</v>
+      </c>
+      <c r="BR43" s="425" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS43" s="426" t="s">
+        <v>102</v>
+      </c>
+      <c r="BT43" s="427" t="s">
+        <v>102</v>
+      </c>
+      <c r="BU43" s="428" t="s">
+        <v>102</v>
       </c>
       <c r="BV43" s="2"/>
       <c r="BW43" s="2"/>
@@ -12484,15 +12480,156 @@
       <c r="DD43" s="2"/>
       <c r="DE43" s="2"/>
     </row>
+    <row r="44" spans="1:109" x14ac:dyDescent="0.8">
+      <c r="A44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="259" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" s="260" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" s="260"/>
+      <c r="E44" s="261"/>
+      <c r="F44" s="262" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2"/>
+      <c r="T44" s="2"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="2"/>
+      <c r="W44" s="2"/>
+      <c r="X44" s="2"/>
+      <c r="Y44" s="2"/>
+      <c r="Z44" s="2"/>
+      <c r="AA44" s="2"/>
+      <c r="AB44" s="2"/>
+      <c r="AC44" s="2"/>
+      <c r="AD44" s="2"/>
+      <c r="AE44" s="2"/>
+      <c r="AF44" s="2"/>
+      <c r="AG44" s="2"/>
+      <c r="AH44" s="2"/>
+      <c r="AI44" s="2"/>
+      <c r="AJ44" s="2"/>
+      <c r="AK44" s="2"/>
+      <c r="AL44" s="2"/>
+      <c r="AM44" s="2"/>
+      <c r="AN44" s="2"/>
+      <c r="AO44" s="2"/>
+      <c r="AP44" s="2"/>
+      <c r="AQ44" s="2"/>
+      <c r="AR44" s="2"/>
+      <c r="AS44" s="2"/>
+      <c r="AT44" s="2"/>
+      <c r="AU44" s="2"/>
+      <c r="AV44" s="2"/>
+      <c r="AW44" s="2"/>
+      <c r="AX44" s="2"/>
+      <c r="AY44" s="2"/>
+      <c r="AZ44" s="2"/>
+      <c r="BA44" s="2"/>
+      <c r="BB44" s="2"/>
+      <c r="BC44" s="2"/>
+      <c r="BD44" s="2"/>
+      <c r="BE44" s="2"/>
+      <c r="BF44" s="2"/>
+      <c r="BG44" s="2"/>
+      <c r="BH44" s="2"/>
+      <c r="BI44" s="2"/>
+      <c r="BJ44" s="2"/>
+      <c r="BK44" s="429" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL44" s="430" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM44" s="431" t="s">
+        <v>104</v>
+      </c>
+      <c r="BN44" s="432" t="s">
+        <v>104</v>
+      </c>
+      <c r="BO44" s="433" t="s">
+        <v>104</v>
+      </c>
+      <c r="BP44" s="434" t="s">
+        <v>104</v>
+      </c>
+      <c r="BQ44" s="435" t="s">
+        <v>104</v>
+      </c>
+      <c r="BR44" s="436" t="s">
+        <v>104</v>
+      </c>
+      <c r="BS44" s="437" t="s">
+        <v>104</v>
+      </c>
+      <c r="BT44" s="438" t="s">
+        <v>104</v>
+      </c>
+      <c r="BU44" s="439" t="s">
+        <v>104</v>
+      </c>
+      <c r="BV44" s="2"/>
+      <c r="BW44" s="2"/>
+      <c r="BX44" s="2"/>
+      <c r="BY44" s="2"/>
+      <c r="BZ44" s="2"/>
+      <c r="CA44" s="2"/>
+      <c r="CB44" s="2"/>
+      <c r="CC44" s="2"/>
+      <c r="CD44" s="2"/>
+      <c r="CE44" s="2"/>
+      <c r="CF44" s="2"/>
+      <c r="CG44" s="2"/>
+      <c r="CH44" s="2"/>
+      <c r="CI44" s="2"/>
+      <c r="CJ44" s="2"/>
+      <c r="CK44" s="2"/>
+      <c r="CL44" s="2"/>
+      <c r="CM44" s="2"/>
+      <c r="CN44" s="2"/>
+      <c r="CO44" s="2"/>
+      <c r="CP44" s="2"/>
+      <c r="CQ44" s="2"/>
+      <c r="CR44" s="2"/>
+      <c r="CS44" s="2"/>
+      <c r="CT44" s="2"/>
+      <c r="CU44" s="2"/>
+      <c r="CV44" s="2"/>
+      <c r="CW44" s="2"/>
+      <c r="CX44" s="2"/>
+      <c r="CY44" s="2"/>
+      <c r="CZ44" s="2"/>
+      <c r="DA44" s="2"/>
+      <c r="DB44" s="2"/>
+      <c r="DC44" s="2"/>
+      <c r="DD44" s="2"/>
+      <c r="DE44" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="43">
     <mergeCell ref="CB2:DE2"/>
     <mergeCell ref="X25:AE25"/>
     <mergeCell ref="X26:AE26"/>
     <mergeCell ref="AE28:AL28"/>
-    <mergeCell ref="BD41:BL41"/>
-    <mergeCell ref="BK42:BU42"/>
+    <mergeCell ref="BD42:BL42"/>
     <mergeCell ref="BK43:BU43"/>
+    <mergeCell ref="BK44:BU44"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="G2:R2"/>
     <mergeCell ref="S2:AW2"/>
@@ -12502,14 +12639,15 @@
     <mergeCell ref="AE33:AL33"/>
     <mergeCell ref="AE31:AL31"/>
     <mergeCell ref="AE32:AL32"/>
-    <mergeCell ref="AS36:AZ36"/>
-    <mergeCell ref="AZ37:BN37"/>
+    <mergeCell ref="AD35:AK35"/>
+    <mergeCell ref="AS37:AZ37"/>
     <mergeCell ref="AZ38:BN38"/>
     <mergeCell ref="AZ39:BN39"/>
     <mergeCell ref="AZ40:BN40"/>
+    <mergeCell ref="AZ41:BN41"/>
     <mergeCell ref="X27:AE27"/>
     <mergeCell ref="AD34:AK34"/>
-    <mergeCell ref="AJ35:AQ35"/>
+    <mergeCell ref="AJ36:AQ36"/>
     <mergeCell ref="Q19:X19"/>
     <mergeCell ref="Q22:X22"/>
     <mergeCell ref="Q21:X21"/>
@@ -12531,7 +12669,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="F1:DE4 A1:C4 F5 H5:DE5 F6:H6 F8:DE14 W7:DE7 F7:I7 A8:C11 B7 B5:C5 A14:C14 A13 B16:C16 A12:B12 F16:P16 F24:DE24 R17:DE17 A15 A18:C18 A17:B17 F15:N15 R15:DE15 A24 F19:DE19 F22:P22 R22:DE22 F17:P18 R18:DE18 R6:DE6 A22:C22 C6 F34:DE34 A35:C43 B27:C27 F27:W27 AF27:DE27 A34 F35:DE43 F33:AB33 AP33:DE33 R16:DE16" numberStoredAsText="1"/>
+    <ignoredError sqref="F1:DE4 A1:C4 F5 H5:DE5 F6:H6 F8:DE14 W7:DE7 F7:I7 A8:C11 B7 B5:C5 A14:C14 A13 B16:C16 A12:B12 F16:P16 F24:DE24 R17:DE17 A15 A18:C18 A17:B17 F15:N15 R15:DE15 A24 F19:DE19 F22:P22 R22:DE22 F17:P18 R18:DE18 R6:DE6 A22:C22 C6 F34:DE34 A36:C44 B27:C27 F27:W27 AF27:DE27 A34 F36:DE44 F33:AB33 AP33:DE33 R16:DE16" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>